--- a/sports_forms/011_vote_for_favorite_coaches--sports_forms.xlsx
+++ b/sports_forms/011_vote_for_favorite_coaches--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>favorite_coach_id_1</t>
+          <t>coach_1_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Coach 1</t>
+          <t>Coach 1 Info</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>favorite_coach_id_2</t>
+          <t>coach_2_info</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Coach 2</t>
+          <t>Coach 2 Info</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>favorite_coach_id_3</t>
+          <t>coach_3_info</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Coach 3</t>
+          <t>Coach 3 Info</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>coach_id_1</t>
+          <t>additional_feedback</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Coach 1</t>
+          <t>Additional Feedback</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>coach_id_2</t>
+          <t>coach_1_feedback</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Coach 2</t>
+          <t>Coach 1 Feedback</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>coach_id_3</t>
+          <t>coach_2_feedback</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Coach 3</t>
+          <t>Coach 2 Feedback</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>vote_for_coach_id</t>
+          <t>coach_3_feedback</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vote For Coach</t>
+          <t>Coach 3 Feedback</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,16 +750,200 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>coach_1_name</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>coach_1_team</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>coach_1_bio</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bio</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>coach_2_name</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Coach 2 Name</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>coach_2_team</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Coach 2 Team</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>coach_2_bio</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Coach 2 Bio</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>coach_3_name</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Coach 3 Name</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>coach_3_team</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Coach 3 Team</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>coach_3_bio</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Coach 3 Bio</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -776,12 +960,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>coach_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Coach 1</t>
         </is>
       </c>
     </row>
@@ -826,12 +1010,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>coach_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Coach 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>favorite_coach_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coach_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Coach 3</t>
         </is>
       </c>
     </row>
